--- a/artfynd/A 37800-2021 artfynd.xlsx
+++ b/artfynd/A 37800-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37800-2021 artfynd.xlsx
+++ b/artfynd/A 37800-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2984048</v>
+        <v>104973</v>
       </c>
       <c r="B2" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sörhagen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567168.2827603326</v>
+        <v>567178</v>
       </c>
       <c r="R2" t="n">
-        <v>6615773.528622316</v>
+        <v>6615814</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,24 +743,9 @@
           <t>2010-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Betade hagmarker fram till 1962, enligt ortsbefolkningen. Sedan fritt igenvuxet. Spridda förekomster. De flesta mer eller mindre överblommade.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Örtrik blandskog, gläntor.</t>
+          <t>Örtrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,53 +782,63 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2593589</v>
+        <v>66361719</v>
       </c>
       <c r="B3" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörhagen, Vstm</t>
+          <t>Åhagen, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567168.2827603326</v>
+        <v>567183</v>
       </c>
       <c r="R3" t="n">
-        <v>6615773.528622316</v>
+        <v>6615821</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-07-13</t>
+          <t>2017-06-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-07-13</t>
+          <t>2017-06-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,23 +889,236 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog, örtrik</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2984048</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörhagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6615774</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Betade hagmarker fram till 1962, enligt ortsbefolkningen. Sedan fritt igenvuxet. Spridda förekomster. De flesta mer eller mindre överblommade.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrik blandskog, gläntor.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2593589</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörhagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567168</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615774</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-07-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog, örtrik</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
